--- a/CLEAR_Master_2026.xlsx
+++ b/CLEAR_Master_2026.xlsx
@@ -67431,7 +67431,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -67951,7 +67951,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -68007,7 +68007,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>cronograma</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -68263,7 +68263,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -68416,14 +68416,14 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>cronograma</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -68520,14 +68520,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -68832,10 +68832,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -68858,14 +68858,14 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>cronograma</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -68910,7 +68910,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
         <v>8</v>
@@ -68988,14 +68988,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>cronograma</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -69352,14 +69352,14 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>cronograma</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -69430,14 +69430,14 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>cronograma</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -69482,14 +69482,14 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>cronograma</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -69745,7 +69745,7 @@
         <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -69820,14 +69820,14 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -70184,14 +70184,14 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>cronograma_sem_prazo</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -70291,7 +70291,7 @@
         <v>6</v>
       </c>
       <c r="D114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -70369,7 +70369,7 @@
         <v>7</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -70548,14 +70548,14 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>cronograma</t>
+          <t>sem_data_no_cronograma</t>
         </is>
       </c>
       <c r="F124" t="n">
